--- a/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
@@ -766,10 +766,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -821,22 +821,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -983,22 +983,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -1100,22 +1100,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -1334,22 +1334,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1455,22 +1455,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>02/12/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>TRIADA GAP BENEFITS</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>TRIADA GAP BENEFITS</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>02/12/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -1578,22 +1578,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>02/12/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>TRIADA GAP BENEFITS</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>TRIADA GAP BENEFITS</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>02/12/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1697,22 +1697,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>02/13/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>02/13/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>02/17/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>02/17/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1927,22 +1927,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>02/18/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>02/18/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2044,22 +2044,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>02/18/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>02/18/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2161,22 +2161,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>02/20/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>02/20/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -2274,22 +2274,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>02/20/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>02/20/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -2416,10 +2416,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -2471,22 +2471,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -2637,22 +2637,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Tricare for Life (All Regions)</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Tricare for Life (All Regions)</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>02/10/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -2756,22 +2756,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>02/10/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -2877,22 +2877,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>02/13/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Tricare for Life (All Regions)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Tricare for Life (All Regions)</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>02/13/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -3008,22 +3008,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>AARP United Healthcare</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>02/16/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -3143,22 +3143,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>AARP United Healthcare</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>02/16/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>SILAC INSURANCE</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>SILAC INSURANCE</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>02/16/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -3397,22 +3397,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>02/18/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Mercy Care RBHA</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>02/18/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -3514,22 +3514,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>02/23/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>DME Region C</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>DME Region C</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>02/23/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -3639,22 +3639,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>02/16/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -3760,22 +3760,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>02/19/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>02/19/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -3881,22 +3881,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>02/11/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>02/11/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -4144,10 +4144,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -4199,22 +4199,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -4365,22 +4365,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -4500,22 +4500,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -4762,22 +4762,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -4889,22 +4889,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -5020,22 +5020,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -5155,22 +5155,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>COMBINED INSURANCE CO OF AMERICA</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -5290,22 +5290,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -5423,22 +5423,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -5548,22 +5548,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -5677,22 +5677,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -5802,22 +5802,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -5927,22 +5927,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -6048,22 +6048,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>02/16/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -6177,22 +6177,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>02/16/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -6310,22 +6310,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>02/16/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -6435,22 +6435,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>02/16/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -6568,22 +6568,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>02/16/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -6701,22 +6701,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>02/16/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -6826,22 +6826,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>02/16/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -6955,22 +6955,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>02/16/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -7084,22 +7084,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>02/16/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>02/16/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -7238,10 +7238,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -7293,22 +7293,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -7459,22 +7459,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>02/17/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Physicians Mutual Insurance Company - ENS</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Physicians Mutual Insurance Company - ENS</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>02/17/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -7582,22 +7582,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>02/20/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>02/20/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -7697,22 +7697,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>02/26/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Mutual of Omaha Medicare Advantage OFAP</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Mutual of Omaha Medicare Advantage OFAP</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>02/26/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -7828,22 +7828,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>02/26/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>Mutual of Omaha Medicare Advantage OFAP</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Mutual of Omaha Medicare Advantage OFAP</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>02/26/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -7955,22 +7955,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>02/26/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Mutual of Omaha Medicare Advantage OFAP</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Mutual of Omaha Medicare Advantage OFAP</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>02/26/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -8086,22 +8086,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -8203,22 +8203,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -8320,22 +8320,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>02/19/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>02/19/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -8449,22 +8449,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>02/26/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>02/26/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -8574,22 +8574,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>02/26/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>02/26/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -8695,22 +8695,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>02/27/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>02/27/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -8812,22 +8812,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Arizona Complete Health (Centene)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -8929,22 +8929,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -9048,22 +9048,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -9167,22 +9167,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -9286,22 +9286,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>02/26/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>02/26/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -9426,10 +9426,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -9481,22 +9481,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -9647,22 +9647,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -9778,22 +9778,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>02/12/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>AARP United Healthcare</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>02/12/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -9897,22 +9897,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>02/12/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>AARP United Healthcare</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>02/12/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -10016,22 +10016,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>02/17/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>AARP United Healthcare</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>02/17/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -10135,22 +10135,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>02/18/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>02/18/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -10254,22 +10254,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>02/12/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>02/12/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">

--- a/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AI2" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ2" s="5" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="AI3" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ3" s="5" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AI4" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ4" s="5" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AI5" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ5" s="5" t="n">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AI6" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ6" s="5" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="AI7" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AI10" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ10" s="5" t="n">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="AI11" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ11" s="5" t="n">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AI10" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ10" s="5" t="n">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="AI18" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AI19" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ19" s="5" t="n">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="AI20" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AI21" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ21" s="5" t="n">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="AI22" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ22" s="5" t="n">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AI23" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ23" s="5" t="n">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="AI7" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="AI8" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ8" s="5" t="n">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="AI10" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ10" s="5" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AI11" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ11" s="5" t="n">
@@ -9250,7 +9250,11 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI14" s="9" t="n"/>
+      <c r="AI14" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ14" s="5" t="n">
         <v>86</v>
       </c>
@@ -9371,7 +9375,11 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI15" s="9" t="n"/>
+      <c r="AI15" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ15" s="5" t="n">
         <v>87</v>
       </c>
@@ -9492,7 +9500,11 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI16" s="9" t="n"/>
+      <c r="AI16" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ16" s="5" t="n">
         <v>88</v>
       </c>
@@ -9605,7 +9617,11 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI17" s="9" t="n"/>
+      <c r="AI17" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ17" s="5" t="n">
         <v>461</v>
       </c>
@@ -10615,7 +10631,7 @@
       </c>
       <c r="AI7" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ7" s="5" t="n">

--- a/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
@@ -27,10 +27,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="MM/DD/YYYY"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -127,7 +126,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -282,12 +281,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -332,12 +331,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -382,12 +381,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -432,12 +431,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -482,12 +481,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -10674,7 +10673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -10814,7 +10813,7 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "25/06/2026";  Date Worked 1: "12/08/2026".</t>
+          <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Date Worked 1: "08/12/2026".</t>
         </is>
       </c>
     </row>
@@ -10831,46 +10830,39 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Both are real dates displayed DD/MM/YYYY. Processed Date is already filled in on the 13 claim lines whose Notes recorded one - the Note still carries the original wording, so nothing was lost. Date Worked 1 starts empty.</t>
+          <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Processed Date is already filled in on the 13 claim lines whose Notes recorded one - the Note still carries the original wording, so nothing was lost. Date Worked 1 starts empty.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Careful when typing into them: Excel reads what you type using its own date setting, not the DD/MM/YYYY the cell displays. On a US Excel, typing 06/25/2026 gives 25 June and the cell then shows 25/06/2026. Type the date the way your Excel expects it and let the cell do the formatting, or check the formula bar afterwards. Every other date column in these files is MM/DD/YYYY, as in the source data.</t>
-        </is>
-      </c>
+      <c r="A26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr"/>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>How this file feeds the master</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>How this file feeds the master</t>
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 1,086 claim lines for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 1,086 claim lines for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+          <t>The link is matched on Line ID (last column), not on row position, so sorting and filtering these sheets is safe. Do not edit or delete the Line ID column, and do not rename the specialty sheet tabs.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>The link is matched on Line ID (last column), not on row position, so sorting and filtering these sheets is safe. Do not edit or delete the Line ID column, and do not rename the specialty sheet tabs.</t>
-        </is>
-      </c>
+      <c r="A30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Everything else in this file is a static copy of the source data from 'Specialty Claims Pending 2026-S1.xlsx' (sheet 'Merged').</t>
         </is>
